--- a/Files/Data/Property Portfolio Data.xlsx
+++ b/Files/Data/Property Portfolio Data.xlsx
@@ -5,17 +5,17 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tmail-merge-with-vue-docx-editor-and-spreadsheet\Files\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EJ2\Samples\presale_demo\mail-merge-with-vue-docx-editor-and-spreadsheet\Files\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE689D0B-02BA-4D02-BB3C-32CAB74597AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E548D21C-8AF0-4021-8AC0-7C3B026B3398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Property Information" sheetId="1" r:id="rId1"/>
     <sheet name="Rent Roll Data" sheetId="2" r:id="rId2"/>
-    <sheet name="Appraisal Summary" sheetId="4" r:id="rId3"/>
+    <sheet name="Appraisal Summary" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -241,58 +241,58 @@
     <t>Tenant 6</t>
   </si>
   <si>
+    <t>T007</t>
+  </si>
+  <si>
+    <t>Tenant 7</t>
+  </si>
+  <si>
+    <t>T008</t>
+  </si>
+  <si>
+    <t>Tenant 8</t>
+  </si>
+  <si>
+    <t>Consulting</t>
+  </si>
+  <si>
+    <t>T009</t>
+  </si>
+  <si>
+    <t>Tenant 9</t>
+  </si>
+  <si>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>T010</t>
+  </si>
+  <si>
+    <t>Tenant 10</t>
+  </si>
+  <si>
+    <t>T011</t>
+  </si>
+  <si>
+    <t>Tenant 11</t>
+  </si>
+  <si>
+    <t>T012</t>
+  </si>
+  <si>
+    <t>Tenant 12</t>
+  </si>
+  <si>
+    <t>T013</t>
+  </si>
+  <si>
+    <t>Tenant 13</t>
+  </si>
+  <si>
+    <t>Marketing</t>
+  </si>
+  <si>
     <t>Vacant</t>
-  </si>
-  <si>
-    <t>T007</t>
-  </si>
-  <si>
-    <t>Tenant 7</t>
-  </si>
-  <si>
-    <t>T008</t>
-  </si>
-  <si>
-    <t>Tenant 8</t>
-  </si>
-  <si>
-    <t>Consulting</t>
-  </si>
-  <si>
-    <t>T009</t>
-  </si>
-  <si>
-    <t>Tenant 9</t>
-  </si>
-  <si>
-    <t>Technology</t>
-  </si>
-  <si>
-    <t>T010</t>
-  </si>
-  <si>
-    <t>Tenant 10</t>
-  </si>
-  <si>
-    <t>T011</t>
-  </si>
-  <si>
-    <t>Tenant 11</t>
-  </si>
-  <si>
-    <t>T012</t>
-  </si>
-  <si>
-    <t>Tenant 12</t>
-  </si>
-  <si>
-    <t>T013</t>
-  </si>
-  <si>
-    <t>Tenant 13</t>
-  </si>
-  <si>
-    <t>Marketing</t>
   </si>
   <si>
     <t>T014</t>
@@ -619,8 +619,8 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -638,7 +638,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <fgColor indexed="64"/>
+          <fgColor rgb="FF000000"/>
           <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
@@ -956,90 +956,90 @@
   <dimension ref="A1:U2"/>
   <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.21875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="31" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="33.88671875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5546875" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" customWidth="1"/>
+    <col min="3" max="3" width="23.21875" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" customWidth="1"/>
+    <col min="5" max="5" width="7.44140625" customWidth="1"/>
+    <col min="6" max="6" width="5.21875" customWidth="1"/>
+    <col min="7" max="7" width="8.21875" customWidth="1"/>
+    <col min="9" max="9" width="12.21875" customWidth="1"/>
+    <col min="10" max="10" width="23.21875" customWidth="1"/>
+    <col min="11" max="11" width="22.44140625" customWidth="1"/>
+    <col min="12" max="12" width="15.88671875" customWidth="1"/>
+    <col min="13" max="13" width="15.6640625" customWidth="1"/>
+    <col min="14" max="14" width="15.88671875" customWidth="1"/>
+    <col min="15" max="15" width="16.44140625" customWidth="1"/>
+    <col min="16" max="16" width="17.21875" customWidth="1"/>
+    <col min="17" max="17" width="13.21875" customWidth="1"/>
+    <col min="18" max="18" width="15.109375" customWidth="1"/>
+    <col min="19" max="19" width="31" customWidth="1"/>
+    <col min="20" max="20" width="33.88671875" customWidth="1"/>
+    <col min="21" max="21" width="17.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1098,10 +1098,10 @@
       <c r="R2">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="S2" s="1">
+      <c r="S2" s="2">
         <v>450000</v>
       </c>
-      <c r="T2" s="1">
+      <c r="T2" s="2">
         <v>120000</v>
       </c>
       <c r="U2" t="s">
@@ -1129,28 +1129,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>38</v>
       </c>
       <c r="I1" s="3" t="s">
@@ -1165,22 +1165,22 @@
       <c r="L1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>43</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>48</v>
       </c>
     </row>
@@ -1209,23 +1209,23 @@
       <c r="H2">
         <v>3217</v>
       </c>
-      <c r="I2" s="1">
+      <c r="I2" s="2">
         <v>4398</v>
       </c>
-      <c r="J2" s="1">
+      <c r="J2" s="2">
         <v>426</v>
       </c>
-      <c r="K2" s="1">
+      <c r="K2" s="2">
         <f t="shared" ref="K2:K33" si="0">IF(M2="Occupied",I2+J2,0)</f>
         <v>4824</v>
       </c>
-      <c r="L2" s="1">
+      <c r="L2" s="2">
         <v>8796</v>
       </c>
       <c r="M2" t="s">
         <v>52</v>
       </c>
-      <c r="N2" s="1">
+      <c r="N2" s="2">
         <f t="shared" ref="N2:N33" si="1">K2*12</f>
         <v>57888</v>
       </c>
@@ -1265,23 +1265,23 @@
       <c r="H3">
         <v>1145</v>
       </c>
-      <c r="I3" s="1">
+      <c r="I3" s="2">
         <v>5634</v>
       </c>
-      <c r="J3" s="1">
+      <c r="J3" s="2">
         <v>790</v>
       </c>
-      <c r="K3" s="1">
+      <c r="K3" s="2">
         <f t="shared" si="0"/>
         <v>6424</v>
       </c>
-      <c r="L3" s="1">
+      <c r="L3" s="2">
         <v>11268</v>
       </c>
       <c r="M3" t="s">
         <v>52</v>
       </c>
-      <c r="N3" s="1">
+      <c r="N3" s="2">
         <f t="shared" si="1"/>
         <v>77088</v>
       </c>
@@ -1321,23 +1321,23 @@
       <c r="H4">
         <v>2727</v>
       </c>
-      <c r="I4" s="1">
+      <c r="I4" s="2">
         <v>3753</v>
       </c>
-      <c r="J4" s="1">
+      <c r="J4" s="2">
         <v>156</v>
       </c>
-      <c r="K4" s="1">
+      <c r="K4" s="2">
         <f t="shared" si="0"/>
         <v>3909</v>
       </c>
-      <c r="L4" s="1">
+      <c r="L4" s="2">
         <v>7506</v>
       </c>
       <c r="M4" t="s">
         <v>52</v>
       </c>
-      <c r="N4" s="1">
+      <c r="N4" s="2">
         <f t="shared" si="1"/>
         <v>46908</v>
       </c>
@@ -1377,23 +1377,23 @@
       <c r="H5">
         <v>1269</v>
       </c>
-      <c r="I5" s="1">
+      <c r="I5" s="2">
         <v>2768</v>
       </c>
-      <c r="J5" s="1">
+      <c r="J5" s="2">
         <v>280</v>
       </c>
-      <c r="K5" s="1">
+      <c r="K5" s="2">
         <f t="shared" si="0"/>
         <v>3048</v>
       </c>
-      <c r="L5" s="1">
+      <c r="L5" s="2">
         <v>5536</v>
       </c>
       <c r="M5" t="s">
         <v>52</v>
       </c>
-      <c r="N5" s="1">
+      <c r="N5" s="2">
         <f t="shared" si="1"/>
         <v>36576</v>
       </c>
@@ -1433,23 +1433,23 @@
       <c r="H6">
         <v>1571</v>
       </c>
-      <c r="I6" s="1">
+      <c r="I6" s="2">
         <v>4891</v>
       </c>
-      <c r="J6" s="1">
+      <c r="J6" s="2">
         <v>169</v>
       </c>
-      <c r="K6" s="1">
+      <c r="K6" s="2">
         <f t="shared" si="0"/>
         <v>5060</v>
       </c>
-      <c r="L6" s="1">
+      <c r="L6" s="2">
         <v>9782</v>
       </c>
       <c r="M6" t="s">
         <v>52</v>
       </c>
-      <c r="N6" s="1">
+      <c r="N6" s="2">
         <f t="shared" si="1"/>
         <v>60720</v>
       </c>
@@ -1489,23 +1489,23 @@
       <c r="H7">
         <v>1619</v>
       </c>
-      <c r="I7" s="1">
+      <c r="I7" s="2">
         <v>3267</v>
       </c>
-      <c r="J7" s="1">
+      <c r="J7" s="2">
         <v>186</v>
       </c>
-      <c r="K7" s="1">
+      <c r="K7" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L7" s="1">
+      <c r="L7" s="2">
         <v>8250</v>
       </c>
       <c r="M7" t="s">
-        <v>68</v>
-      </c>
-      <c r="N7" s="1">
+        <v>85</v>
+      </c>
+      <c r="N7" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1525,10 +1525,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" t="s">
         <v>69</v>
-      </c>
-      <c r="C8" t="s">
-        <v>70</v>
       </c>
       <c r="D8" t="s">
         <v>63</v>
@@ -1545,23 +1545,23 @@
       <c r="H8">
         <v>3059</v>
       </c>
-      <c r="I8" s="1">
+      <c r="I8" s="2">
         <v>5852</v>
       </c>
-      <c r="J8" s="1">
+      <c r="J8" s="2">
         <v>316</v>
       </c>
-      <c r="K8" s="1">
+      <c r="K8" s="2">
         <f t="shared" si="0"/>
         <v>6168</v>
       </c>
-      <c r="L8" s="1">
+      <c r="L8" s="2">
         <v>11704</v>
       </c>
       <c r="M8" t="s">
         <v>52</v>
       </c>
-      <c r="N8" s="1">
+      <c r="N8" s="2">
         <f t="shared" si="1"/>
         <v>74016</v>
       </c>
@@ -1581,13 +1581,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" t="s">
         <v>71</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>72</v>
-      </c>
-      <c r="D9" t="s">
-        <v>73</v>
       </c>
       <c r="E9" s="4">
         <v>45292</v>
@@ -1601,23 +1601,23 @@
       <c r="H9">
         <v>3257</v>
       </c>
-      <c r="I9" s="1">
+      <c r="I9" s="2">
         <v>2940</v>
       </c>
-      <c r="J9" s="1">
+      <c r="J9" s="2">
         <v>539</v>
       </c>
-      <c r="K9" s="1">
+      <c r="K9" s="2">
         <f t="shared" si="0"/>
         <v>3479</v>
       </c>
-      <c r="L9" s="1">
+      <c r="L9" s="2">
         <v>5880</v>
       </c>
       <c r="M9" t="s">
         <v>52</v>
       </c>
-      <c r="N9" s="1">
+      <c r="N9" s="2">
         <f t="shared" si="1"/>
         <v>41748</v>
       </c>
@@ -1637,13 +1637,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" t="s">
         <v>74</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>75</v>
-      </c>
-      <c r="D10" t="s">
-        <v>76</v>
       </c>
       <c r="E10" s="4">
         <v>45292</v>
@@ -1657,23 +1657,23 @@
       <c r="H10">
         <v>1523</v>
       </c>
-      <c r="I10" s="1">
+      <c r="I10" s="2">
         <v>4339</v>
       </c>
-      <c r="J10" s="1">
+      <c r="J10" s="2">
         <v>798</v>
       </c>
-      <c r="K10" s="1">
+      <c r="K10" s="2">
         <f t="shared" si="0"/>
         <v>5137</v>
       </c>
-      <c r="L10" s="1">
+      <c r="L10" s="2">
         <v>8678</v>
       </c>
       <c r="M10" t="s">
         <v>52</v>
       </c>
-      <c r="N10" s="1">
+      <c r="N10" s="2">
         <f t="shared" si="1"/>
         <v>61644</v>
       </c>
@@ -1693,10 +1693,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C11" t="s">
         <v>77</v>
-      </c>
-      <c r="C11" t="s">
-        <v>78</v>
       </c>
       <c r="D11" t="s">
         <v>63</v>
@@ -1713,23 +1713,23 @@
       <c r="H11">
         <v>2788</v>
       </c>
-      <c r="I11" s="1">
+      <c r="I11" s="2">
         <v>4793</v>
       </c>
-      <c r="J11" s="1">
+      <c r="J11" s="2">
         <v>519</v>
       </c>
-      <c r="K11" s="1">
+      <c r="K11" s="2">
         <f t="shared" si="0"/>
         <v>5312</v>
       </c>
-      <c r="L11" s="1">
+      <c r="L11" s="2">
         <v>9586</v>
       </c>
       <c r="M11" t="s">
         <v>52</v>
       </c>
-      <c r="N11" s="1">
+      <c r="N11" s="2">
         <f t="shared" si="1"/>
         <v>63744</v>
       </c>
@@ -1749,10 +1749,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C12" t="s">
         <v>79</v>
-      </c>
-      <c r="C12" t="s">
-        <v>80</v>
       </c>
       <c r="D12" t="s">
         <v>56</v>
@@ -1769,23 +1769,23 @@
       <c r="H12">
         <v>2240</v>
       </c>
-      <c r="I12" s="1">
+      <c r="I12" s="2">
         <v>4235</v>
       </c>
-      <c r="J12" s="1">
+      <c r="J12" s="2">
         <v>145</v>
       </c>
-      <c r="K12" s="1">
+      <c r="K12" s="2">
         <f t="shared" si="0"/>
         <v>4380</v>
       </c>
-      <c r="L12" s="1">
+      <c r="L12" s="2">
         <v>8470</v>
       </c>
       <c r="M12" t="s">
         <v>52</v>
       </c>
-      <c r="N12" s="1">
+      <c r="N12" s="2">
         <f t="shared" si="1"/>
         <v>52560</v>
       </c>
@@ -1805,13 +1805,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" t="s">
         <v>81</v>
       </c>
-      <c r="C13" t="s">
-        <v>82</v>
-      </c>
       <c r="D13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E13" s="4">
         <v>45292</v>
@@ -1825,23 +1825,23 @@
       <c r="H13">
         <v>2200</v>
       </c>
-      <c r="I13" s="1">
+      <c r="I13" s="2">
         <v>3756</v>
       </c>
-      <c r="J13" s="1">
+      <c r="J13" s="2">
         <v>698</v>
       </c>
-      <c r="K13" s="1">
+      <c r="K13" s="2">
         <f t="shared" si="0"/>
         <v>4454</v>
       </c>
-      <c r="L13" s="1">
+      <c r="L13" s="2">
         <v>7512</v>
       </c>
       <c r="M13" t="s">
         <v>52</v>
       </c>
-      <c r="N13" s="1">
+      <c r="N13" s="2">
         <f t="shared" si="1"/>
         <v>53448</v>
       </c>
@@ -1861,13 +1861,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>82</v>
+      </c>
+      <c r="C14" t="s">
         <v>83</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>84</v>
-      </c>
-      <c r="D14" t="s">
-        <v>85</v>
       </c>
       <c r="E14" s="4">
         <v>45292</v>
@@ -1881,23 +1881,23 @@
       <c r="H14">
         <v>1137</v>
       </c>
-      <c r="I14" s="1">
+      <c r="I14" s="2">
         <v>2469</v>
       </c>
-      <c r="J14" s="1">
+      <c r="J14" s="2">
         <v>136</v>
       </c>
-      <c r="K14" s="1">
+      <c r="K14" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L14" s="1">
+      <c r="L14" s="2">
         <v>5437</v>
       </c>
       <c r="M14" t="s">
-        <v>68</v>
-      </c>
-      <c r="N14" s="1">
+        <v>85</v>
+      </c>
+      <c r="N14" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1923,7 +1923,7 @@
         <v>87</v>
       </c>
       <c r="D15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E15" s="4">
         <v>45292</v>
@@ -1937,23 +1937,23 @@
       <c r="H15">
         <v>1067</v>
       </c>
-      <c r="I15" s="1">
+      <c r="I15" s="2">
         <v>5082</v>
       </c>
-      <c r="J15" s="1">
+      <c r="J15" s="2">
         <v>134</v>
       </c>
-      <c r="K15" s="1">
+      <c r="K15" s="2">
         <f t="shared" si="0"/>
         <v>5216</v>
       </c>
-      <c r="L15" s="1">
+      <c r="L15" s="2">
         <v>10164</v>
       </c>
       <c r="M15" t="s">
         <v>52</v>
       </c>
-      <c r="N15" s="1">
+      <c r="N15" s="2">
         <f t="shared" si="1"/>
         <v>62592</v>
       </c>
@@ -1979,7 +1979,7 @@
         <v>89</v>
       </c>
       <c r="D16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E16" s="4">
         <v>45292</v>
@@ -1993,23 +1993,23 @@
       <c r="H16">
         <v>1415</v>
       </c>
-      <c r="I16" s="1">
+      <c r="I16" s="2">
         <v>1909</v>
       </c>
-      <c r="J16" s="1">
+      <c r="J16" s="2">
         <v>629</v>
       </c>
-      <c r="K16" s="1">
+      <c r="K16" s="2">
         <f t="shared" si="0"/>
         <v>2538</v>
       </c>
-      <c r="L16" s="1">
+      <c r="L16" s="2">
         <v>3818</v>
       </c>
       <c r="M16" t="s">
         <v>52</v>
       </c>
-      <c r="N16" s="1">
+      <c r="N16" s="2">
         <f t="shared" si="1"/>
         <v>30456</v>
       </c>
@@ -2035,7 +2035,7 @@
         <v>91</v>
       </c>
       <c r="D17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E17" s="4">
         <v>45292</v>
@@ -2049,23 +2049,23 @@
       <c r="H17">
         <v>2885</v>
       </c>
-      <c r="I17" s="1">
+      <c r="I17" s="2">
         <v>5879</v>
       </c>
-      <c r="J17" s="1">
+      <c r="J17" s="2">
         <v>356</v>
       </c>
-      <c r="K17" s="1">
+      <c r="K17" s="2">
         <f t="shared" si="0"/>
         <v>6235</v>
       </c>
-      <c r="L17" s="1">
+      <c r="L17" s="2">
         <v>11758</v>
       </c>
       <c r="M17" t="s">
         <v>52</v>
       </c>
-      <c r="N17" s="1">
+      <c r="N17" s="2">
         <f t="shared" si="1"/>
         <v>74820</v>
       </c>
@@ -2091,7 +2091,7 @@
         <v>93</v>
       </c>
       <c r="D18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E18" s="4">
         <v>45292</v>
@@ -2105,23 +2105,23 @@
       <c r="H18">
         <v>1813</v>
       </c>
-      <c r="I18" s="1">
+      <c r="I18" s="2">
         <v>3393</v>
       </c>
-      <c r="J18" s="1">
+      <c r="J18" s="2">
         <v>149</v>
       </c>
-      <c r="K18" s="1">
+      <c r="K18" s="2">
         <f t="shared" si="0"/>
         <v>3542</v>
       </c>
-      <c r="L18" s="1">
+      <c r="L18" s="2">
         <v>6786</v>
       </c>
       <c r="M18" t="s">
         <v>52</v>
       </c>
-      <c r="N18" s="1">
+      <c r="N18" s="2">
         <f t="shared" si="1"/>
         <v>42504</v>
       </c>
@@ -2147,7 +2147,7 @@
         <v>95</v>
       </c>
       <c r="D19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E19" s="4">
         <v>45292</v>
@@ -2161,23 +2161,23 @@
       <c r="H19">
         <v>2019</v>
       </c>
-      <c r="I19" s="1">
+      <c r="I19" s="2">
         <v>3011</v>
       </c>
-      <c r="J19" s="1">
+      <c r="J19" s="2">
         <v>796</v>
       </c>
-      <c r="K19" s="1">
+      <c r="K19" s="2">
         <f t="shared" si="0"/>
         <v>3807</v>
       </c>
-      <c r="L19" s="1">
+      <c r="L19" s="2">
         <v>6022</v>
       </c>
       <c r="M19" t="s">
         <v>52</v>
       </c>
-      <c r="N19" s="1">
+      <c r="N19" s="2">
         <f t="shared" si="1"/>
         <v>45684</v>
       </c>
@@ -2217,23 +2217,23 @@
       <c r="H20">
         <v>3026</v>
       </c>
-      <c r="I20" s="1">
+      <c r="I20" s="2">
         <v>4722</v>
       </c>
-      <c r="J20" s="1">
+      <c r="J20" s="2">
         <v>256</v>
       </c>
-      <c r="K20" s="1">
+      <c r="K20" s="2">
         <f t="shared" si="0"/>
         <v>4978</v>
       </c>
-      <c r="L20" s="1">
+      <c r="L20" s="2">
         <v>9444</v>
       </c>
       <c r="M20" t="s">
         <v>52</v>
       </c>
-      <c r="N20" s="1">
+      <c r="N20" s="2">
         <f t="shared" si="1"/>
         <v>59736</v>
       </c>
@@ -2259,7 +2259,7 @@
         <v>99</v>
       </c>
       <c r="D21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E21" s="4">
         <v>45292</v>
@@ -2273,23 +2273,23 @@
       <c r="H21">
         <v>2524</v>
       </c>
-      <c r="I21" s="1">
+      <c r="I21" s="2">
         <v>4899</v>
       </c>
-      <c r="J21" s="1">
+      <c r="J21" s="2">
         <v>215</v>
       </c>
-      <c r="K21" s="1">
+      <c r="K21" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L21" s="1">
+      <c r="L21" s="2">
         <v>8600</v>
       </c>
       <c r="M21" t="s">
-        <v>68</v>
-      </c>
-      <c r="N21" s="1">
+        <v>85</v>
+      </c>
+      <c r="N21" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2329,23 +2329,23 @@
       <c r="H22">
         <v>3107</v>
       </c>
-      <c r="I22" s="1">
+      <c r="I22" s="2">
         <v>5151</v>
       </c>
-      <c r="J22" s="1">
+      <c r="J22" s="2">
         <v>428</v>
       </c>
-      <c r="K22" s="1">
+      <c r="K22" s="2">
         <f t="shared" si="0"/>
         <v>5579</v>
       </c>
-      <c r="L22" s="1">
+      <c r="L22" s="2">
         <v>10302</v>
       </c>
       <c r="M22" t="s">
         <v>52</v>
       </c>
-      <c r="N22" s="1">
+      <c r="N22" s="2">
         <f t="shared" si="1"/>
         <v>66948</v>
       </c>
@@ -2371,7 +2371,7 @@
         <v>103</v>
       </c>
       <c r="D23" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E23" s="4">
         <v>45292</v>
@@ -2385,23 +2385,23 @@
       <c r="H23">
         <v>1261</v>
       </c>
-      <c r="I23" s="1">
+      <c r="I23" s="2">
         <v>5618</v>
       </c>
-      <c r="J23" s="1">
+      <c r="J23" s="2">
         <v>551</v>
       </c>
-      <c r="K23" s="1">
+      <c r="K23" s="2">
         <f t="shared" si="0"/>
         <v>6169</v>
       </c>
-      <c r="L23" s="1">
+      <c r="L23" s="2">
         <v>11236</v>
       </c>
       <c r="M23" t="s">
         <v>52</v>
       </c>
-      <c r="N23" s="1">
+      <c r="N23" s="2">
         <f t="shared" si="1"/>
         <v>74028</v>
       </c>
@@ -2441,23 +2441,23 @@
       <c r="H24">
         <v>1268</v>
       </c>
-      <c r="I24" s="1">
+      <c r="I24" s="2">
         <v>5465</v>
       </c>
-      <c r="J24" s="1">
+      <c r="J24" s="2">
         <v>688</v>
       </c>
-      <c r="K24" s="1">
+      <c r="K24" s="2">
         <f t="shared" si="0"/>
         <v>6153</v>
       </c>
-      <c r="L24" s="1">
+      <c r="L24" s="2">
         <v>10930</v>
       </c>
       <c r="M24" t="s">
         <v>52</v>
       </c>
-      <c r="N24" s="1">
+      <c r="N24" s="2">
         <f t="shared" si="1"/>
         <v>73836</v>
       </c>
@@ -2497,23 +2497,23 @@
       <c r="H25">
         <v>2559</v>
       </c>
-      <c r="I25" s="1">
+      <c r="I25" s="2">
         <v>2678</v>
       </c>
-      <c r="J25" s="1">
+      <c r="J25" s="2">
         <v>607</v>
       </c>
-      <c r="K25" s="1">
+      <c r="K25" s="2">
         <f t="shared" si="0"/>
         <v>3285</v>
       </c>
-      <c r="L25" s="1">
+      <c r="L25" s="2">
         <v>5356</v>
       </c>
       <c r="M25" t="s">
         <v>52</v>
       </c>
-      <c r="N25" s="1">
+      <c r="N25" s="2">
         <f t="shared" si="1"/>
         <v>39420</v>
       </c>
@@ -2539,7 +2539,7 @@
         <v>109</v>
       </c>
       <c r="D26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E26" s="4">
         <v>45292</v>
@@ -2553,23 +2553,23 @@
       <c r="H26">
         <v>1017</v>
       </c>
-      <c r="I26" s="1">
+      <c r="I26" s="2">
         <v>5719</v>
       </c>
-      <c r="J26" s="1">
+      <c r="J26" s="2">
         <v>591</v>
       </c>
-      <c r="K26" s="1">
+      <c r="K26" s="2">
         <f t="shared" si="0"/>
         <v>6310</v>
       </c>
-      <c r="L26" s="1">
+      <c r="L26" s="2">
         <v>11438</v>
       </c>
       <c r="M26" t="s">
         <v>52</v>
       </c>
-      <c r="N26" s="1">
+      <c r="N26" s="2">
         <f t="shared" si="1"/>
         <v>75720</v>
       </c>
@@ -2609,23 +2609,23 @@
       <c r="H27">
         <v>3351</v>
       </c>
-      <c r="I27" s="1">
+      <c r="I27" s="2">
         <v>1964</v>
       </c>
-      <c r="J27" s="1">
+      <c r="J27" s="2">
         <v>571</v>
       </c>
-      <c r="K27" s="1">
+      <c r="K27" s="2">
         <f t="shared" si="0"/>
         <v>2535</v>
       </c>
-      <c r="L27" s="1">
+      <c r="L27" s="2">
         <v>3928</v>
       </c>
       <c r="M27" t="s">
         <v>52</v>
       </c>
-      <c r="N27" s="1">
+      <c r="N27" s="2">
         <f t="shared" si="1"/>
         <v>30420</v>
       </c>
@@ -2651,7 +2651,7 @@
         <v>113</v>
       </c>
       <c r="D28" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E28" s="4">
         <v>45292</v>
@@ -2665,23 +2665,23 @@
       <c r="H28">
         <v>2306</v>
       </c>
-      <c r="I28" s="1">
+      <c r="I28" s="2">
         <v>5215</v>
       </c>
-      <c r="J28" s="1">
+      <c r="J28" s="2">
         <v>269</v>
       </c>
-      <c r="K28" s="1">
+      <c r="K28" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L28" s="1">
+      <c r="L28" s="2">
         <v>8125</v>
       </c>
       <c r="M28" t="s">
-        <v>68</v>
-      </c>
-      <c r="N28" s="1">
+        <v>85</v>
+      </c>
+      <c r="N28" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2707,7 +2707,7 @@
         <v>115</v>
       </c>
       <c r="D29" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E29" s="4">
         <v>45292</v>
@@ -2721,23 +2721,23 @@
       <c r="H29">
         <v>2895</v>
       </c>
-      <c r="I29" s="1">
+      <c r="I29" s="2">
         <v>2248</v>
       </c>
-      <c r="J29" s="1">
+      <c r="J29" s="2">
         <v>708</v>
       </c>
-      <c r="K29" s="1">
+      <c r="K29" s="2">
         <f t="shared" si="0"/>
         <v>2956</v>
       </c>
-      <c r="L29" s="1">
+      <c r="L29" s="2">
         <v>4496</v>
       </c>
       <c r="M29" t="s">
         <v>52</v>
       </c>
-      <c r="N29" s="1">
+      <c r="N29" s="2">
         <f t="shared" si="1"/>
         <v>35472</v>
       </c>
@@ -2777,23 +2777,23 @@
       <c r="H30">
         <v>1664</v>
       </c>
-      <c r="I30" s="1">
+      <c r="I30" s="2">
         <v>2946</v>
       </c>
-      <c r="J30" s="1">
+      <c r="J30" s="2">
         <v>219</v>
       </c>
-      <c r="K30" s="1">
+      <c r="K30" s="2">
         <f t="shared" si="0"/>
         <v>3165</v>
       </c>
-      <c r="L30" s="1">
+      <c r="L30" s="2">
         <v>5892</v>
       </c>
       <c r="M30" t="s">
         <v>52</v>
       </c>
-      <c r="N30" s="1">
+      <c r="N30" s="2">
         <f t="shared" si="1"/>
         <v>37980</v>
       </c>
@@ -2833,23 +2833,23 @@
       <c r="H31">
         <v>2127</v>
       </c>
-      <c r="I31" s="1">
+      <c r="I31" s="2">
         <v>5614</v>
       </c>
-      <c r="J31" s="1">
+      <c r="J31" s="2">
         <v>584</v>
       </c>
-      <c r="K31" s="1">
+      <c r="K31" s="2">
         <f t="shared" si="0"/>
         <v>6198</v>
       </c>
-      <c r="L31" s="1">
+      <c r="L31" s="2">
         <v>11228</v>
       </c>
       <c r="M31" t="s">
         <v>52</v>
       </c>
-      <c r="N31" s="1">
+      <c r="N31" s="2">
         <f t="shared" si="1"/>
         <v>74376</v>
       </c>
@@ -2889,23 +2889,23 @@
       <c r="H32">
         <v>3043</v>
       </c>
-      <c r="I32" s="1">
+      <c r="I32" s="2">
         <v>2409</v>
       </c>
-      <c r="J32" s="1">
+      <c r="J32" s="2">
         <v>711</v>
       </c>
-      <c r="K32" s="1">
+      <c r="K32" s="2">
         <f t="shared" si="0"/>
         <v>3120</v>
       </c>
-      <c r="L32" s="1">
+      <c r="L32" s="2">
         <v>4818</v>
       </c>
       <c r="M32" t="s">
         <v>52</v>
       </c>
-      <c r="N32" s="1">
+      <c r="N32" s="2">
         <f t="shared" si="1"/>
         <v>37440</v>
       </c>
@@ -2931,7 +2931,7 @@
         <v>123</v>
       </c>
       <c r="D33" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E33" s="4">
         <v>45292</v>
@@ -2945,23 +2945,23 @@
       <c r="H33">
         <v>804</v>
       </c>
-      <c r="I33" s="1">
+      <c r="I33" s="2">
         <v>3992</v>
       </c>
-      <c r="J33" s="1">
+      <c r="J33" s="2">
         <v>226</v>
       </c>
-      <c r="K33" s="1">
+      <c r="K33" s="2">
         <f t="shared" si="0"/>
         <v>4218</v>
       </c>
-      <c r="L33" s="1">
+      <c r="L33" s="2">
         <v>7984</v>
       </c>
       <c r="M33" t="s">
         <v>52</v>
       </c>
-      <c r="N33" s="1">
+      <c r="N33" s="2">
         <f t="shared" si="1"/>
         <v>50616</v>
       </c>
@@ -3001,23 +3001,23 @@
       <c r="H34">
         <v>886</v>
       </c>
-      <c r="I34" s="1">
+      <c r="I34" s="2">
         <v>5631</v>
       </c>
-      <c r="J34" s="1">
+      <c r="J34" s="2">
         <v>579</v>
       </c>
-      <c r="K34" s="1">
-        <f t="shared" ref="K34:K51" si="3">IF(M34="Occupied",I34+J34,0)</f>
+      <c r="K34" s="2">
+        <f t="shared" ref="K34:K65" si="3">IF(M34="Occupied",I34+J34,0)</f>
         <v>6210</v>
       </c>
-      <c r="L34" s="1">
+      <c r="L34" s="2">
         <v>11262</v>
       </c>
       <c r="M34" t="s">
         <v>52</v>
       </c>
-      <c r="N34" s="1">
+      <c r="N34" s="2">
         <f t="shared" ref="N34:N51" si="4">K34*12</f>
         <v>74520</v>
       </c>
@@ -3043,7 +3043,7 @@
         <v>127</v>
       </c>
       <c r="D35" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E35" s="4">
         <v>45292</v>
@@ -3057,23 +3057,23 @@
       <c r="H35">
         <v>2111</v>
       </c>
-      <c r="I35" s="1">
+      <c r="I35" s="2">
         <v>4999</v>
       </c>
-      <c r="J35" s="1">
+      <c r="J35" s="2">
         <v>299</v>
       </c>
-      <c r="K35" s="1">
+      <c r="K35" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L35" s="1">
+      <c r="L35" s="2">
         <v>7599</v>
       </c>
       <c r="M35" t="s">
-        <v>68</v>
-      </c>
-      <c r="N35" s="1">
+        <v>85</v>
+      </c>
+      <c r="N35" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -3113,23 +3113,23 @@
       <c r="H36">
         <v>1222</v>
       </c>
-      <c r="I36" s="1">
+      <c r="I36" s="2">
         <v>3236</v>
       </c>
-      <c r="J36" s="1">
+      <c r="J36" s="2">
         <v>241</v>
       </c>
-      <c r="K36" s="1">
+      <c r="K36" s="2">
         <f t="shared" si="3"/>
         <v>3477</v>
       </c>
-      <c r="L36" s="1">
+      <c r="L36" s="2">
         <v>6472</v>
       </c>
       <c r="M36" t="s">
         <v>52</v>
       </c>
-      <c r="N36" s="1">
+      <c r="N36" s="2">
         <f t="shared" si="4"/>
         <v>41724</v>
       </c>
@@ -3155,7 +3155,7 @@
         <v>131</v>
       </c>
       <c r="D37" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E37" s="4">
         <v>45292</v>
@@ -3169,23 +3169,23 @@
       <c r="H37">
         <v>2411</v>
       </c>
-      <c r="I37" s="1">
+      <c r="I37" s="2">
         <v>3781</v>
       </c>
-      <c r="J37" s="1">
+      <c r="J37" s="2">
         <v>784</v>
       </c>
-      <c r="K37" s="1">
+      <c r="K37" s="2">
         <f t="shared" si="3"/>
         <v>4565</v>
       </c>
-      <c r="L37" s="1">
+      <c r="L37" s="2">
         <v>7562</v>
       </c>
       <c r="M37" t="s">
         <v>52</v>
       </c>
-      <c r="N37" s="1">
+      <c r="N37" s="2">
         <f t="shared" si="4"/>
         <v>54780</v>
       </c>
@@ -3211,7 +3211,7 @@
         <v>133</v>
       </c>
       <c r="D38" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E38" s="4">
         <v>45292</v>
@@ -3225,23 +3225,23 @@
       <c r="H38">
         <v>1213</v>
       </c>
-      <c r="I38" s="1">
+      <c r="I38" s="2">
         <v>3249</v>
       </c>
-      <c r="J38" s="1">
+      <c r="J38" s="2">
         <v>554</v>
       </c>
-      <c r="K38" s="1">
+      <c r="K38" s="2">
         <f t="shared" si="3"/>
         <v>3803</v>
       </c>
-      <c r="L38" s="1">
+      <c r="L38" s="2">
         <v>6498</v>
       </c>
       <c r="M38" t="s">
         <v>52</v>
       </c>
-      <c r="N38" s="1">
+      <c r="N38" s="2">
         <f t="shared" si="4"/>
         <v>45636</v>
       </c>
@@ -3281,23 +3281,23 @@
       <c r="H39">
         <v>1416</v>
       </c>
-      <c r="I39" s="1">
+      <c r="I39" s="2">
         <v>4355</v>
       </c>
-      <c r="J39" s="1">
+      <c r="J39" s="2">
         <v>104</v>
       </c>
-      <c r="K39" s="1">
+      <c r="K39" s="2">
         <f t="shared" si="3"/>
         <v>4459</v>
       </c>
-      <c r="L39" s="1">
+      <c r="L39" s="2">
         <v>8710</v>
       </c>
       <c r="M39" t="s">
         <v>52</v>
       </c>
-      <c r="N39" s="1">
+      <c r="N39" s="2">
         <f t="shared" si="4"/>
         <v>53508</v>
       </c>
@@ -3323,7 +3323,7 @@
         <v>137</v>
       </c>
       <c r="D40" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E40" s="4">
         <v>45292</v>
@@ -3337,23 +3337,23 @@
       <c r="H40">
         <v>1716</v>
       </c>
-      <c r="I40" s="1">
+      <c r="I40" s="2">
         <v>3745</v>
       </c>
-      <c r="J40" s="1">
+      <c r="J40" s="2">
         <v>368</v>
       </c>
-      <c r="K40" s="1">
+      <c r="K40" s="2">
         <f t="shared" si="3"/>
         <v>4113</v>
       </c>
-      <c r="L40" s="1">
+      <c r="L40" s="2">
         <v>7490</v>
       </c>
       <c r="M40" t="s">
         <v>52</v>
       </c>
-      <c r="N40" s="1">
+      <c r="N40" s="2">
         <f t="shared" si="4"/>
         <v>49356</v>
       </c>
@@ -3393,23 +3393,23 @@
       <c r="H41">
         <v>3042</v>
       </c>
-      <c r="I41" s="1">
+      <c r="I41" s="2">
         <v>2928</v>
       </c>
-      <c r="J41" s="1">
+      <c r="J41" s="2">
         <v>756</v>
       </c>
-      <c r="K41" s="1">
+      <c r="K41" s="2">
         <f t="shared" si="3"/>
         <v>3684</v>
       </c>
-      <c r="L41" s="1">
+      <c r="L41" s="2">
         <v>5856</v>
       </c>
       <c r="M41" t="s">
         <v>52</v>
       </c>
-      <c r="N41" s="1">
+      <c r="N41" s="2">
         <f t="shared" si="4"/>
         <v>44208</v>
       </c>
@@ -3435,7 +3435,7 @@
         <v>141</v>
       </c>
       <c r="D42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E42" s="4">
         <v>45292</v>
@@ -3449,23 +3449,23 @@
       <c r="H42">
         <v>2807</v>
       </c>
-      <c r="I42" s="1">
+      <c r="I42" s="2">
         <v>5988</v>
       </c>
-      <c r="J42" s="1">
+      <c r="J42" s="2">
         <v>266</v>
       </c>
-      <c r="K42" s="1">
+      <c r="K42" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L42" s="1">
+      <c r="L42" s="2">
         <v>8122</v>
       </c>
       <c r="M42" t="s">
-        <v>68</v>
-      </c>
-      <c r="N42" s="1">
+        <v>85</v>
+      </c>
+      <c r="N42" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -3491,7 +3491,7 @@
         <v>143</v>
       </c>
       <c r="D43" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E43" s="4">
         <v>45292</v>
@@ -3505,23 +3505,23 @@
       <c r="H43">
         <v>1856</v>
       </c>
-      <c r="I43" s="1">
+      <c r="I43" s="2">
         <v>2347</v>
       </c>
-      <c r="J43" s="1">
+      <c r="J43" s="2">
         <v>654</v>
       </c>
-      <c r="K43" s="1">
+      <c r="K43" s="2">
         <f t="shared" si="3"/>
         <v>3001</v>
       </c>
-      <c r="L43" s="1">
+      <c r="L43" s="2">
         <v>4694</v>
       </c>
       <c r="M43" t="s">
         <v>52</v>
       </c>
-      <c r="N43" s="1">
+      <c r="N43" s="2">
         <f t="shared" si="4"/>
         <v>36012</v>
       </c>
@@ -3561,23 +3561,23 @@
       <c r="H44">
         <v>1118</v>
       </c>
-      <c r="I44" s="1">
+      <c r="I44" s="2">
         <v>5404</v>
       </c>
-      <c r="J44" s="1">
+      <c r="J44" s="2">
         <v>720</v>
       </c>
-      <c r="K44" s="1">
+      <c r="K44" s="2">
         <f t="shared" si="3"/>
         <v>6124</v>
       </c>
-      <c r="L44" s="1">
+      <c r="L44" s="2">
         <v>10808</v>
       </c>
       <c r="M44" t="s">
         <v>52</v>
       </c>
-      <c r="N44" s="1">
+      <c r="N44" s="2">
         <f t="shared" si="4"/>
         <v>73488</v>
       </c>
@@ -3617,23 +3617,23 @@
       <c r="H45">
         <v>2542</v>
       </c>
-      <c r="I45" s="1">
+      <c r="I45" s="2">
         <v>2244</v>
       </c>
-      <c r="J45" s="1">
+      <c r="J45" s="2">
         <v>252</v>
       </c>
-      <c r="K45" s="1">
+      <c r="K45" s="2">
         <f t="shared" si="3"/>
         <v>2496</v>
       </c>
-      <c r="L45" s="1">
+      <c r="L45" s="2">
         <v>4488</v>
       </c>
       <c r="M45" t="s">
         <v>52</v>
       </c>
-      <c r="N45" s="1">
+      <c r="N45" s="2">
         <f t="shared" si="4"/>
         <v>29952</v>
       </c>
@@ -3659,7 +3659,7 @@
         <v>149</v>
       </c>
       <c r="D46" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E46" s="4">
         <v>45292</v>
@@ -3673,23 +3673,23 @@
       <c r="H46">
         <v>887</v>
       </c>
-      <c r="I46" s="1">
+      <c r="I46" s="2">
         <v>5607</v>
       </c>
-      <c r="J46" s="1">
+      <c r="J46" s="2">
         <v>546</v>
       </c>
-      <c r="K46" s="1">
+      <c r="K46" s="2">
         <f t="shared" si="3"/>
         <v>6153</v>
       </c>
-      <c r="L46" s="1">
+      <c r="L46" s="2">
         <v>11214</v>
       </c>
       <c r="M46" t="s">
         <v>52</v>
       </c>
-      <c r="N46" s="1">
+      <c r="N46" s="2">
         <f t="shared" si="4"/>
         <v>73836</v>
       </c>
@@ -3729,23 +3729,23 @@
       <c r="H47">
         <v>3203</v>
       </c>
-      <c r="I47" s="1">
+      <c r="I47" s="2">
         <v>5340</v>
       </c>
-      <c r="J47" s="1">
+      <c r="J47" s="2">
         <v>437</v>
       </c>
-      <c r="K47" s="1">
+      <c r="K47" s="2">
         <f t="shared" si="3"/>
         <v>5777</v>
       </c>
-      <c r="L47" s="1">
+      <c r="L47" s="2">
         <v>10680</v>
       </c>
       <c r="M47" t="s">
         <v>52</v>
       </c>
-      <c r="N47" s="1">
+      <c r="N47" s="2">
         <f t="shared" si="4"/>
         <v>69324</v>
       </c>
@@ -3771,7 +3771,7 @@
         <v>153</v>
       </c>
       <c r="D48" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E48" s="4">
         <v>45292</v>
@@ -3785,23 +3785,23 @@
       <c r="H48">
         <v>2490</v>
       </c>
-      <c r="I48" s="1">
+      <c r="I48" s="2">
         <v>4870</v>
       </c>
-      <c r="J48" s="1">
+      <c r="J48" s="2">
         <v>437</v>
       </c>
-      <c r="K48" s="1">
+      <c r="K48" s="2">
         <f t="shared" si="3"/>
         <v>5307</v>
       </c>
-      <c r="L48" s="1">
+      <c r="L48" s="2">
         <v>9740</v>
       </c>
       <c r="M48" t="s">
         <v>52</v>
       </c>
-      <c r="N48" s="1">
+      <c r="N48" s="2">
         <f t="shared" si="4"/>
         <v>63684</v>
       </c>
@@ -3827,7 +3827,7 @@
         <v>155</v>
       </c>
       <c r="D49" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E49" s="4">
         <v>45292</v>
@@ -3841,23 +3841,23 @@
       <c r="H49">
         <v>2883</v>
       </c>
-      <c r="I49" s="1">
+      <c r="I49" s="2">
         <v>4988</v>
       </c>
-      <c r="J49" s="1">
+      <c r="J49" s="2">
         <v>275</v>
       </c>
-      <c r="K49" s="1">
+      <c r="K49" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L49" s="1">
+      <c r="L49" s="2">
         <v>7899</v>
       </c>
       <c r="M49" t="s">
-        <v>68</v>
-      </c>
-      <c r="N49" s="1">
+        <v>85</v>
+      </c>
+      <c r="N49" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -3883,7 +3883,7 @@
         <v>157</v>
       </c>
       <c r="D50" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E50" s="4">
         <v>45292</v>
@@ -3897,23 +3897,23 @@
       <c r="H50">
         <v>2181</v>
       </c>
-      <c r="I50" s="1">
+      <c r="I50" s="2">
         <v>2059</v>
       </c>
-      <c r="J50" s="1">
+      <c r="J50" s="2">
         <v>514</v>
       </c>
-      <c r="K50" s="1">
+      <c r="K50" s="2">
         <f t="shared" si="3"/>
         <v>2573</v>
       </c>
-      <c r="L50" s="1">
+      <c r="L50" s="2">
         <v>4118</v>
       </c>
       <c r="M50" t="s">
         <v>52</v>
       </c>
-      <c r="N50" s="1">
+      <c r="N50" s="2">
         <f t="shared" si="4"/>
         <v>30876</v>
       </c>
@@ -3953,23 +3953,23 @@
       <c r="H51">
         <v>966</v>
       </c>
-      <c r="I51" s="1">
+      <c r="I51" s="2">
         <v>4890</v>
       </c>
-      <c r="J51" s="1">
+      <c r="J51" s="2">
         <v>308</v>
       </c>
-      <c r="K51" s="1">
+      <c r="K51" s="2">
         <f t="shared" si="3"/>
         <v>5198</v>
       </c>
-      <c r="L51" s="1">
+      <c r="L51" s="2">
         <v>9780</v>
       </c>
       <c r="M51" t="s">
         <v>52</v>
       </c>
-      <c r="N51" s="1">
+      <c r="N51" s="2">
         <f t="shared" si="4"/>
         <v>62376</v>
       </c>
@@ -3996,63 +3996,63 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8924A27-8E13-4836-A9ED-5420714EE9B4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.88671875" customWidth="1"/>
+    <col min="2" max="2" width="13.21875" customWidth="1"/>
+    <col min="3" max="3" width="11.21875" customWidth="1"/>
+    <col min="4" max="4" width="19.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" customWidth="1"/>
+    <col min="6" max="6" width="15.5546875" customWidth="1"/>
+    <col min="7" max="7" width="19.21875" customWidth="1"/>
+    <col min="8" max="8" width="14.44140625" customWidth="1"/>
+    <col min="9" max="9" width="17.44140625" customWidth="1"/>
+    <col min="10" max="10" width="17" customWidth="1"/>
+    <col min="11" max="11" width="19.6640625" customWidth="1"/>
+    <col min="12" max="12" width="12.44140625" customWidth="1"/>
+    <col min="13" max="13" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>172</v>
       </c>
     </row>
@@ -4073,15 +4073,15 @@
         <f>B2/A2</f>
         <v>0.86</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="2">
         <f>SUM('Rent Roll Data'!K2:K51)</f>
         <v>195139</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2" s="2">
         <f>SUM('Rent Roll Data'!N2:N51)</f>
         <v>2341668</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="2">
         <f ca="1">AVERAGE('Rent Roll Data'!A11:AX11)</f>
         <v>14934.408333333333</v>
       </c>
@@ -4089,28 +4089,29 @@
         <f>MAX('Rent Roll Data'!H2:H51)</f>
         <v>3351</v>
       </c>
-      <c r="I2" s="1">
+      <c r="I2" s="2">
         <f>MAX('Rent Roll Data'!N2:N51)</f>
         <v>77088</v>
       </c>
-      <c r="J2" s="1">
+      <c r="J2" s="2">
         <f>'Property Information'!S2</f>
         <v>450000</v>
       </c>
-      <c r="K2" s="1">
+      <c r="K2" s="2">
         <f>'Property Information'!T2</f>
         <v>120000</v>
       </c>
-      <c r="L2" s="1">
+      <c r="L2" s="2">
         <f>F2-(J2+K2)</f>
         <v>1771668</v>
       </c>
-      <c r="M2" s="1">
+      <c r="M2" s="2">
         <f>L2/'Property Information'!R2</f>
         <v>27256430.769230768</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
--- a/Files/Data/Property Portfolio Data.xlsx
+++ b/Files/Data/Property Portfolio Data.xlsx
@@ -1,41 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EJ2\Samples\presale_demo\mail-merge-with-vue-docx-editor-and-spreadsheet\Files\Data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E548D21C-8AF0-4021-8AC0-7C3B026B3398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Property Information" sheetId="1" r:id="rId1"/>
     <sheet name="Rent Roll Data" sheetId="2" r:id="rId2"/>
     <sheet name="Appraisal Summary" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr fullPrecision="1" calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="173" count="312">
   <si>
     <t>Property ID</t>
   </si>
@@ -241,6 +222,9 @@
     <t>Tenant 6</t>
   </si>
   <si>
+    <t>Vacant</t>
+  </si>
+  <si>
     <t>T007</t>
   </si>
   <si>
@@ -290,9 +274,6 @@
   </si>
   <si>
     <t>Marketing</t>
-  </si>
-  <si>
-    <t>Vacant</t>
   </si>
   <si>
     <t>T014</t>
@@ -559,32 +540,56 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <charset val="0"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <charset val="0"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill patternType="none">
+        <fgColor indexed="64"/>
+        <bgColor indexed="65"/>
+      </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="gray125">
+        <fgColor indexed="64"/>
+        <bgColor indexed="65"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -602,40 +607,65 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="7">
+  <cellStyleXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFont="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFont="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFont="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFont="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFont="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="7">
-    <cellStyle name="Appraisal SummaryLockedColumnStyle" xfId="5" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
-    <cellStyle name="Appraisal SummaryUnLockedColumnStyle" xfId="6" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+  <cellStyles count="12">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Property InformationLockedColumnStyle" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="Property InformationUnLockedColumnStyle" xfId="2" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
-    <cellStyle name="Rent Roll DataLockedColumnStyle" xfId="3" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
-    <cellStyle name="Rent Roll DataUnLockedColumnStyle" xfId="4" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Property InformationLockedColumnStyle" xfId="20"/>
+    <cellStyle name="Property InformationUnLockedColumnStyle" xfId="21"/>
+    <cellStyle name="Rent Roll DataLockedColumnStyle" xfId="22"/>
+    <cellStyle name="Rent Roll DataUnLockedColumnStyle" xfId="23"/>
+    <cellStyle name="Appraisal SummaryLockedColumnStyle" xfId="24"/>
+    <cellStyle name="Appraisal SummaryUnLockedColumnStyle" xfId="25"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
+      <font/>
       <fill>
         <patternFill>
           <fgColor rgb="FF000000"/>
@@ -645,340 +675,38 @@
     </dxf>
   </dxfs>
   <tableStyles count="0"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="44546A"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4472C4"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="ED7D31"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="FFC000"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="70AD47"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0563C1"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="954F72"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
-      <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr customHeight="true" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.5546875" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" customWidth="1"/>
-    <col min="3" max="3" width="23.21875" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" customWidth="1"/>
-    <col min="5" max="5" width="7.44140625" customWidth="1"/>
-    <col min="6" max="6" width="5.21875" customWidth="1"/>
-    <col min="7" max="7" width="8.21875" customWidth="1"/>
-    <col min="9" max="9" width="12.21875" customWidth="1"/>
-    <col min="10" max="10" width="23.21875" customWidth="1"/>
-    <col min="11" max="11" width="22.44140625" customWidth="1"/>
-    <col min="12" max="12" width="15.88671875" customWidth="1"/>
-    <col min="13" max="13" width="15.6640625" customWidth="1"/>
-    <col min="14" max="14" width="15.88671875" customWidth="1"/>
-    <col min="15" max="15" width="16.44140625" customWidth="1"/>
-    <col min="16" max="16" width="17.21875" customWidth="1"/>
-    <col min="17" max="17" width="13.21875" customWidth="1"/>
-    <col min="18" max="18" width="15.109375" customWidth="1"/>
+    <col min="1" max="1" width="10.5703125" customWidth="1"/>
+    <col min="2" max="2" width="13.84765625" customWidth="1"/>
+    <col min="3" max="3" width="23.27734375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="7.41796875" customWidth="1"/>
+    <col min="6" max="6" width="5.27734375" customWidth="1"/>
+    <col min="7" max="7" width="8.27734375" customWidth="1"/>
+    <col min="9" max="9" width="12.27734375" customWidth="1"/>
+    <col min="10" max="10" width="23.27734375" customWidth="1"/>
+    <col min="11" max="11" width="22.41796875" customWidth="1"/>
+    <col min="12" max="12" width="15.84765625" customWidth="1"/>
+    <col min="13" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="14" width="15.84765625" customWidth="1"/>
+    <col min="15" max="15" width="16.41796875" customWidth="1"/>
+    <col min="16" max="16" width="17.27734375" customWidth="1"/>
+    <col min="17" max="17" width="13.27734375" customWidth="1"/>
+    <col min="18" max="18" width="15.140625" customWidth="1"/>
     <col min="19" max="19" width="31" customWidth="1"/>
-    <col min="20" max="20" width="33.88671875" customWidth="1"/>
-    <col min="21" max="21" width="17.21875" customWidth="1"/>
+    <col min="20" max="20" width="33.84765625" customWidth="1"/>
+    <col min="21" max="21" width="17.27734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1043,7 +771,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -1096,7 +824,7 @@
         <v>46301</v>
       </c>
       <c r="R2">
-        <v>6.5000000000000002E-2</v>
+        <v>0.065</v>
       </c>
       <c r="S2" s="2">
         <v>450000</v>
@@ -1110,25 +838,27 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter alignWithMargins="0"/>
+  <headerFooter scaleWithDoc="1" alignWithMargins="0" differentFirst="0" differentOddEven="0"/>
+  <extLst/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr/>
   <dimension ref="A1:R51"/>
-  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr customHeight="true" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" customWidth="1"/>
     <col min="2" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="18.5546875" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
     <col min="7" max="14" width="22" customWidth="1"/>
-    <col min="15" max="15" width="30.6640625" customWidth="1"/>
+    <col min="15" max="15" width="30.7109375" customWidth="1"/>
     <col min="16" max="18" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>31</v>
       </c>
@@ -1184,7 +914,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1216,8 +946,8 @@
         <v>426</v>
       </c>
       <c r="K2" s="2">
-        <f t="shared" ref="K2:K33" si="0">IF(M2="Occupied",I2+J2,0)</f>
-        <v>4824</v>
+        <f ca="1">IF(M2="Occupied",I2+J2,0)</f>
+        <v>0</v>
       </c>
       <c r="L2" s="2">
         <v>8796</v>
@@ -1226,12 +956,12 @@
         <v>52</v>
       </c>
       <c r="N2" s="2">
-        <f t="shared" ref="N2:N33" si="1">K2*12</f>
-        <v>57888</v>
+        <f ca="1">K2*12</f>
+        <v>0</v>
       </c>
       <c r="O2">
-        <f t="shared" ref="O2:O33" ca="1" si="2">DATEDIF(TODAY(),F2,"M")</f>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F2,"M")</f>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0.6</v>
@@ -1240,7 +970,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1272,8 +1002,8 @@
         <v>790</v>
       </c>
       <c r="K3" s="2">
-        <f t="shared" si="0"/>
-        <v>6424</v>
+        <f ca="1">IF(M3="Occupied",I3+J3,0)</f>
+        <v>0</v>
       </c>
       <c r="L3" s="2">
         <v>11268</v>
@@ -1282,12 +1012,12 @@
         <v>52</v>
       </c>
       <c r="N3" s="2">
-        <f t="shared" si="1"/>
-        <v>77088</v>
+        <f ca="1">K3*12</f>
+        <v>0</v>
       </c>
       <c r="O3">
-        <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F3,"M")</f>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>0.7</v>
@@ -1296,7 +1026,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1328,8 +1058,8 @@
         <v>156</v>
       </c>
       <c r="K4" s="2">
-        <f t="shared" si="0"/>
-        <v>3909</v>
+        <f ca="1">IF(M4="Occupied",I4+J4,0)</f>
+        <v>0</v>
       </c>
       <c r="L4" s="2">
         <v>7506</v>
@@ -1338,12 +1068,12 @@
         <v>52</v>
       </c>
       <c r="N4" s="2">
-        <f t="shared" si="1"/>
-        <v>46908</v>
+        <f ca="1">K4*12</f>
+        <v>0</v>
       </c>
       <c r="O4">
-        <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F4,"M")</f>
+        <v>0</v>
       </c>
       <c r="P4">
         <v>0.6</v>
@@ -1352,7 +1082,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1384,8 +1114,8 @@
         <v>280</v>
       </c>
       <c r="K5" s="2">
-        <f t="shared" si="0"/>
-        <v>3048</v>
+        <f ca="1">IF(M5="Occupied",I5+J5,0)</f>
+        <v>0</v>
       </c>
       <c r="L5" s="2">
         <v>5536</v>
@@ -1394,12 +1124,12 @@
         <v>52</v>
       </c>
       <c r="N5" s="2">
-        <f t="shared" si="1"/>
-        <v>36576</v>
+        <f ca="1">K5*12</f>
+        <v>0</v>
       </c>
       <c r="O5">
-        <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F5,"M")</f>
+        <v>0</v>
       </c>
       <c r="P5">
         <v>0.6</v>
@@ -1408,7 +1138,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1440,8 +1170,8 @@
         <v>169</v>
       </c>
       <c r="K6" s="2">
-        <f t="shared" si="0"/>
-        <v>5060</v>
+        <f ca="1">IF(M6="Occupied",I6+J6,0)</f>
+        <v>0</v>
       </c>
       <c r="L6" s="2">
         <v>9782</v>
@@ -1450,12 +1180,12 @@
         <v>52</v>
       </c>
       <c r="N6" s="2">
-        <f t="shared" si="1"/>
-        <v>60720</v>
+        <f ca="1">K6*12</f>
+        <v>0</v>
       </c>
       <c r="O6">
-        <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F6,"M")</f>
+        <v>0</v>
       </c>
       <c r="P6">
         <v>0.7</v>
@@ -1464,7 +1194,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1496,22 +1226,22 @@
         <v>186</v>
       </c>
       <c r="K7" s="2">
-        <f t="shared" si="0"/>
+        <f ca="1">IF(M7="Occupied",I7+J7,0)</f>
         <v>0</v>
       </c>
       <c r="L7" s="2">
         <v>8250</v>
       </c>
       <c r="M7" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="N7" s="2">
-        <f t="shared" si="1"/>
+        <f ca="1">K7*12</f>
         <v>0</v>
       </c>
       <c r="O7">
-        <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F7,"M")</f>
+        <v>0</v>
       </c>
       <c r="P7">
         <v>0.8</v>
@@ -1520,15 +1250,15 @@
         <v>53</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D8" t="s">
         <v>63</v>
@@ -1552,8 +1282,8 @@
         <v>316</v>
       </c>
       <c r="K8" s="2">
-        <f t="shared" si="0"/>
-        <v>6168</v>
+        <f ca="1">IF(M8="Occupied",I8+J8,0)</f>
+        <v>0</v>
       </c>
       <c r="L8" s="2">
         <v>11704</v>
@@ -1562,12 +1292,12 @@
         <v>52</v>
       </c>
       <c r="N8" s="2">
-        <f t="shared" si="1"/>
-        <v>74016</v>
+        <f ca="1">K8*12</f>
+        <v>0</v>
       </c>
       <c r="O8">
-        <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F8,"M")</f>
+        <v>0</v>
       </c>
       <c r="P8">
         <v>0.6</v>
@@ -1576,18 +1306,18 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E9" s="4">
         <v>45292</v>
@@ -1608,8 +1338,8 @@
         <v>539</v>
       </c>
       <c r="K9" s="2">
-        <f t="shared" si="0"/>
-        <v>3479</v>
+        <f ca="1">IF(M9="Occupied",I9+J9,0)</f>
+        <v>0</v>
       </c>
       <c r="L9" s="2">
         <v>5880</v>
@@ -1618,12 +1348,12 @@
         <v>52</v>
       </c>
       <c r="N9" s="2">
-        <f t="shared" si="1"/>
-        <v>41748</v>
+        <f ca="1">K9*12</f>
+        <v>0</v>
       </c>
       <c r="O9">
-        <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F9,"M")</f>
+        <v>0</v>
       </c>
       <c r="P9">
         <v>0.6</v>
@@ -1632,18 +1362,18 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E10" s="4">
         <v>45292</v>
@@ -1664,8 +1394,8 @@
         <v>798</v>
       </c>
       <c r="K10" s="2">
-        <f t="shared" si="0"/>
-        <v>5137</v>
+        <f ca="1">IF(M10="Occupied",I10+J10,0)</f>
+        <v>0</v>
       </c>
       <c r="L10" s="2">
         <v>8678</v>
@@ -1674,12 +1404,12 @@
         <v>52</v>
       </c>
       <c r="N10" s="2">
-        <f t="shared" si="1"/>
-        <v>61644</v>
+        <f ca="1">K10*12</f>
+        <v>0</v>
       </c>
       <c r="O10">
-        <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F10,"M")</f>
+        <v>0</v>
       </c>
       <c r="P10">
         <v>0.9</v>
@@ -1688,15 +1418,15 @@
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D11" t="s">
         <v>63</v>
@@ -1720,8 +1450,8 @@
         <v>519</v>
       </c>
       <c r="K11" s="2">
-        <f t="shared" si="0"/>
-        <v>5312</v>
+        <f ca="1">IF(M11="Occupied",I11+J11,0)</f>
+        <v>0</v>
       </c>
       <c r="L11" s="2">
         <v>9586</v>
@@ -1730,12 +1460,12 @@
         <v>52</v>
       </c>
       <c r="N11" s="2">
-        <f t="shared" si="1"/>
-        <v>63744</v>
+        <f ca="1">K11*12</f>
+        <v>0</v>
       </c>
       <c r="O11">
-        <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F11,"M")</f>
+        <v>0</v>
       </c>
       <c r="P11">
         <v>0.9</v>
@@ -1744,15 +1474,15 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D12" t="s">
         <v>56</v>
@@ -1776,8 +1506,8 @@
         <v>145</v>
       </c>
       <c r="K12" s="2">
-        <f t="shared" si="0"/>
-        <v>4380</v>
+        <f ca="1">IF(M12="Occupied",I12+J12,0)</f>
+        <v>0</v>
       </c>
       <c r="L12" s="2">
         <v>8470</v>
@@ -1786,12 +1516,12 @@
         <v>52</v>
       </c>
       <c r="N12" s="2">
-        <f t="shared" si="1"/>
-        <v>52560</v>
+        <f ca="1">K12*12</f>
+        <v>0</v>
       </c>
       <c r="O12">
-        <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F12,"M")</f>
+        <v>0</v>
       </c>
       <c r="P12">
         <v>0.6</v>
@@ -1800,18 +1530,18 @@
         <v>57</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E13" s="4">
         <v>45292</v>
@@ -1832,8 +1562,8 @@
         <v>698</v>
       </c>
       <c r="K13" s="2">
-        <f t="shared" si="0"/>
-        <v>4454</v>
+        <f ca="1">IF(M13="Occupied",I13+J13,0)</f>
+        <v>0</v>
       </c>
       <c r="L13" s="2">
         <v>7512</v>
@@ -1842,12 +1572,12 @@
         <v>52</v>
       </c>
       <c r="N13" s="2">
-        <f t="shared" si="1"/>
-        <v>53448</v>
+        <f ca="1">K13*12</f>
+        <v>0</v>
       </c>
       <c r="O13">
-        <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F13,"M")</f>
+        <v>0</v>
       </c>
       <c r="P13">
         <v>0.9</v>
@@ -1856,18 +1586,18 @@
         <v>57</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E14" s="4">
         <v>45292</v>
@@ -1888,22 +1618,22 @@
         <v>136</v>
       </c>
       <c r="K14" s="2">
-        <f t="shared" si="0"/>
+        <f ca="1">IF(M14="Occupied",I14+J14,0)</f>
         <v>0</v>
       </c>
       <c r="L14" s="2">
         <v>5437</v>
       </c>
       <c r="M14" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="N14" s="2">
-        <f t="shared" si="1"/>
+        <f ca="1">K14*12</f>
         <v>0</v>
       </c>
       <c r="O14">
-        <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F14,"M")</f>
+        <v>0</v>
       </c>
       <c r="P14">
         <v>0.7</v>
@@ -1912,7 +1642,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1923,7 +1653,7 @@
         <v>87</v>
       </c>
       <c r="D15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E15" s="4">
         <v>45292</v>
@@ -1944,8 +1674,8 @@
         <v>134</v>
       </c>
       <c r="K15" s="2">
-        <f t="shared" si="0"/>
-        <v>5216</v>
+        <f ca="1">IF(M15="Occupied",I15+J15,0)</f>
+        <v>0</v>
       </c>
       <c r="L15" s="2">
         <v>10164</v>
@@ -1954,12 +1684,12 @@
         <v>52</v>
       </c>
       <c r="N15" s="2">
-        <f t="shared" si="1"/>
-        <v>62592</v>
+        <f ca="1">K15*12</f>
+        <v>0</v>
       </c>
       <c r="O15">
-        <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F15,"M")</f>
+        <v>0</v>
       </c>
       <c r="P15">
         <v>0.6</v>
@@ -1968,7 +1698,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1979,7 +1709,7 @@
         <v>89</v>
       </c>
       <c r="D16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E16" s="4">
         <v>45292</v>
@@ -2000,8 +1730,8 @@
         <v>629</v>
       </c>
       <c r="K16" s="2">
-        <f t="shared" si="0"/>
-        <v>2538</v>
+        <f ca="1">IF(M16="Occupied",I16+J16,0)</f>
+        <v>0</v>
       </c>
       <c r="L16" s="2">
         <v>3818</v>
@@ -2010,12 +1740,12 @@
         <v>52</v>
       </c>
       <c r="N16" s="2">
-        <f t="shared" si="1"/>
-        <v>30456</v>
+        <f ca="1">K16*12</f>
+        <v>0</v>
       </c>
       <c r="O16">
-        <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F16,"M")</f>
+        <v>0</v>
       </c>
       <c r="P16">
         <v>0.6</v>
@@ -2024,7 +1754,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2035,7 +1765,7 @@
         <v>91</v>
       </c>
       <c r="D17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E17" s="4">
         <v>45292</v>
@@ -2056,8 +1786,8 @@
         <v>356</v>
       </c>
       <c r="K17" s="2">
-        <f t="shared" si="0"/>
-        <v>6235</v>
+        <f ca="1">IF(M17="Occupied",I17+J17,0)</f>
+        <v>0</v>
       </c>
       <c r="L17" s="2">
         <v>11758</v>
@@ -2066,12 +1796,12 @@
         <v>52</v>
       </c>
       <c r="N17" s="2">
-        <f t="shared" si="1"/>
-        <v>74820</v>
+        <f ca="1">K17*12</f>
+        <v>0</v>
       </c>
       <c r="O17">
-        <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F17,"M")</f>
+        <v>0</v>
       </c>
       <c r="P17">
         <v>0.8</v>
@@ -2080,7 +1810,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2091,7 +1821,7 @@
         <v>93</v>
       </c>
       <c r="D18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E18" s="4">
         <v>45292</v>
@@ -2112,8 +1842,8 @@
         <v>149</v>
       </c>
       <c r="K18" s="2">
-        <f t="shared" si="0"/>
-        <v>3542</v>
+        <f ca="1">IF(M18="Occupied",I18+J18,0)</f>
+        <v>0</v>
       </c>
       <c r="L18" s="2">
         <v>6786</v>
@@ -2122,12 +1852,12 @@
         <v>52</v>
       </c>
       <c r="N18" s="2">
-        <f t="shared" si="1"/>
-        <v>42504</v>
+        <f ca="1">K18*12</f>
+        <v>0</v>
       </c>
       <c r="O18">
-        <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F18,"M")</f>
+        <v>0</v>
       </c>
       <c r="P18">
         <v>0.7</v>
@@ -2136,7 +1866,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2147,7 +1877,7 @@
         <v>95</v>
       </c>
       <c r="D19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E19" s="4">
         <v>45292</v>
@@ -2168,8 +1898,8 @@
         <v>796</v>
       </c>
       <c r="K19" s="2">
-        <f t="shared" si="0"/>
-        <v>3807</v>
+        <f ca="1">IF(M19="Occupied",I19+J19,0)</f>
+        <v>0</v>
       </c>
       <c r="L19" s="2">
         <v>6022</v>
@@ -2178,12 +1908,12 @@
         <v>52</v>
       </c>
       <c r="N19" s="2">
-        <f t="shared" si="1"/>
-        <v>45684</v>
+        <f ca="1">K19*12</f>
+        <v>0</v>
       </c>
       <c r="O19">
-        <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F19,"M")</f>
+        <v>0</v>
       </c>
       <c r="P19">
         <v>0.8</v>
@@ -2192,7 +1922,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2224,8 +1954,8 @@
         <v>256</v>
       </c>
       <c r="K20" s="2">
-        <f t="shared" si="0"/>
-        <v>4978</v>
+        <f ca="1">IF(M20="Occupied",I20+J20,0)</f>
+        <v>0</v>
       </c>
       <c r="L20" s="2">
         <v>9444</v>
@@ -2234,12 +1964,12 @@
         <v>52</v>
       </c>
       <c r="N20" s="2">
-        <f t="shared" si="1"/>
-        <v>59736</v>
+        <f ca="1">K20*12</f>
+        <v>0</v>
       </c>
       <c r="O20">
-        <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F20,"M")</f>
+        <v>0</v>
       </c>
       <c r="P20">
         <v>0.7</v>
@@ -2248,7 +1978,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2259,7 +1989,7 @@
         <v>99</v>
       </c>
       <c r="D21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E21" s="4">
         <v>45292</v>
@@ -2280,22 +2010,22 @@
         <v>215</v>
       </c>
       <c r="K21" s="2">
-        <f t="shared" si="0"/>
+        <f ca="1">IF(M21="Occupied",I21+J21,0)</f>
         <v>0</v>
       </c>
       <c r="L21" s="2">
         <v>8600</v>
       </c>
       <c r="M21" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="N21" s="2">
-        <f t="shared" si="1"/>
+        <f ca="1">K21*12</f>
         <v>0</v>
       </c>
       <c r="O21">
-        <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F21,"M")</f>
+        <v>0</v>
       </c>
       <c r="P21">
         <v>0.8</v>
@@ -2304,7 +2034,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2336,8 +2066,8 @@
         <v>428</v>
       </c>
       <c r="K22" s="2">
-        <f t="shared" si="0"/>
-        <v>5579</v>
+        <f ca="1">IF(M22="Occupied",I22+J22,0)</f>
+        <v>0</v>
       </c>
       <c r="L22" s="2">
         <v>10302</v>
@@ -2346,12 +2076,12 @@
         <v>52</v>
       </c>
       <c r="N22" s="2">
-        <f t="shared" si="1"/>
-        <v>66948</v>
+        <f ca="1">K22*12</f>
+        <v>0</v>
       </c>
       <c r="O22">
-        <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F22,"M")</f>
+        <v>0</v>
       </c>
       <c r="P22">
         <v>0.8</v>
@@ -2360,7 +2090,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2371,7 +2101,7 @@
         <v>103</v>
       </c>
       <c r="D23" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E23" s="4">
         <v>45292</v>
@@ -2392,8 +2122,8 @@
         <v>551</v>
       </c>
       <c r="K23" s="2">
-        <f t="shared" si="0"/>
-        <v>6169</v>
+        <f ca="1">IF(M23="Occupied",I23+J23,0)</f>
+        <v>0</v>
       </c>
       <c r="L23" s="2">
         <v>11236</v>
@@ -2402,12 +2132,12 @@
         <v>52</v>
       </c>
       <c r="N23" s="2">
-        <f t="shared" si="1"/>
-        <v>74028</v>
+        <f ca="1">K23*12</f>
+        <v>0</v>
       </c>
       <c r="O23">
-        <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F23,"M")</f>
+        <v>0</v>
       </c>
       <c r="P23">
         <v>0.8</v>
@@ -2416,7 +2146,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2448,8 +2178,8 @@
         <v>688</v>
       </c>
       <c r="K24" s="2">
-        <f t="shared" si="0"/>
-        <v>6153</v>
+        <f ca="1">IF(M24="Occupied",I24+J24,0)</f>
+        <v>0</v>
       </c>
       <c r="L24" s="2">
         <v>10930</v>
@@ -2458,12 +2188,12 @@
         <v>52</v>
       </c>
       <c r="N24" s="2">
-        <f t="shared" si="1"/>
-        <v>73836</v>
+        <f ca="1">K24*12</f>
+        <v>0</v>
       </c>
       <c r="O24">
-        <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F24,"M")</f>
+        <v>0</v>
       </c>
       <c r="P24">
         <v>0.8</v>
@@ -2472,7 +2202,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2504,8 +2234,8 @@
         <v>607</v>
       </c>
       <c r="K25" s="2">
-        <f t="shared" si="0"/>
-        <v>3285</v>
+        <f ca="1">IF(M25="Occupied",I25+J25,0)</f>
+        <v>0</v>
       </c>
       <c r="L25" s="2">
         <v>5356</v>
@@ -2514,12 +2244,12 @@
         <v>52</v>
       </c>
       <c r="N25" s="2">
-        <f t="shared" si="1"/>
-        <v>39420</v>
+        <f ca="1">K25*12</f>
+        <v>0</v>
       </c>
       <c r="O25">
-        <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F25,"M")</f>
+        <v>0</v>
       </c>
       <c r="P25">
         <v>0.6</v>
@@ -2528,7 +2258,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2539,7 +2269,7 @@
         <v>109</v>
       </c>
       <c r="D26" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E26" s="4">
         <v>45292</v>
@@ -2560,8 +2290,8 @@
         <v>591</v>
       </c>
       <c r="K26" s="2">
-        <f t="shared" si="0"/>
-        <v>6310</v>
+        <f ca="1">IF(M26="Occupied",I26+J26,0)</f>
+        <v>0</v>
       </c>
       <c r="L26" s="2">
         <v>11438</v>
@@ -2570,12 +2300,12 @@
         <v>52</v>
       </c>
       <c r="N26" s="2">
-        <f t="shared" si="1"/>
-        <v>75720</v>
+        <f ca="1">K26*12</f>
+        <v>0</v>
       </c>
       <c r="O26">
-        <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F26,"M")</f>
+        <v>0</v>
       </c>
       <c r="P26">
         <v>0.9</v>
@@ -2584,7 +2314,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2616,8 +2346,8 @@
         <v>571</v>
       </c>
       <c r="K27" s="2">
-        <f t="shared" si="0"/>
-        <v>2535</v>
+        <f ca="1">IF(M27="Occupied",I27+J27,0)</f>
+        <v>0</v>
       </c>
       <c r="L27" s="2">
         <v>3928</v>
@@ -2626,12 +2356,12 @@
         <v>52</v>
       </c>
       <c r="N27" s="2">
-        <f t="shared" si="1"/>
-        <v>30420</v>
+        <f ca="1">K27*12</f>
+        <v>0</v>
       </c>
       <c r="O27">
-        <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F27,"M")</f>
+        <v>0</v>
       </c>
       <c r="P27">
         <v>0.7</v>
@@ -2640,7 +2370,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2651,7 +2381,7 @@
         <v>113</v>
       </c>
       <c r="D28" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E28" s="4">
         <v>45292</v>
@@ -2672,22 +2402,22 @@
         <v>269</v>
       </c>
       <c r="K28" s="2">
-        <f t="shared" si="0"/>
+        <f ca="1">IF(M28="Occupied",I28+J28,0)</f>
         <v>0</v>
       </c>
       <c r="L28" s="2">
         <v>8125</v>
       </c>
       <c r="M28" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="N28" s="2">
-        <f t="shared" si="1"/>
+        <f ca="1">K28*12</f>
         <v>0</v>
       </c>
       <c r="O28">
-        <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F28,"M")</f>
+        <v>0</v>
       </c>
       <c r="P28">
         <v>0.7</v>
@@ -2696,7 +2426,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2707,7 +2437,7 @@
         <v>115</v>
       </c>
       <c r="D29" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E29" s="4">
         <v>45292</v>
@@ -2728,8 +2458,8 @@
         <v>708</v>
       </c>
       <c r="K29" s="2">
-        <f t="shared" si="0"/>
-        <v>2956</v>
+        <f ca="1">IF(M29="Occupied",I29+J29,0)</f>
+        <v>0</v>
       </c>
       <c r="L29" s="2">
         <v>4496</v>
@@ -2738,12 +2468,12 @@
         <v>52</v>
       </c>
       <c r="N29" s="2">
-        <f t="shared" si="1"/>
-        <v>35472</v>
+        <f ca="1">K29*12</f>
+        <v>0</v>
       </c>
       <c r="O29">
-        <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F29,"M")</f>
+        <v>0</v>
       </c>
       <c r="P29">
         <v>0.7</v>
@@ -2752,7 +2482,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2784,8 +2514,8 @@
         <v>219</v>
       </c>
       <c r="K30" s="2">
-        <f t="shared" si="0"/>
-        <v>3165</v>
+        <f ca="1">IF(M30="Occupied",I30+J30,0)</f>
+        <v>0</v>
       </c>
       <c r="L30" s="2">
         <v>5892</v>
@@ -2794,12 +2524,12 @@
         <v>52</v>
       </c>
       <c r="N30" s="2">
-        <f t="shared" si="1"/>
-        <v>37980</v>
+        <f ca="1">K30*12</f>
+        <v>0</v>
       </c>
       <c r="O30">
-        <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F30,"M")</f>
+        <v>0</v>
       </c>
       <c r="P30">
         <v>0.6</v>
@@ -2808,7 +2538,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2840,8 +2570,8 @@
         <v>584</v>
       </c>
       <c r="K31" s="2">
-        <f t="shared" si="0"/>
-        <v>6198</v>
+        <f ca="1">IF(M31="Occupied",I31+J31,0)</f>
+        <v>0</v>
       </c>
       <c r="L31" s="2">
         <v>11228</v>
@@ -2850,12 +2580,12 @@
         <v>52</v>
       </c>
       <c r="N31" s="2">
-        <f t="shared" si="1"/>
-        <v>74376</v>
+        <f ca="1">K31*12</f>
+        <v>0</v>
       </c>
       <c r="O31">
-        <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F31,"M")</f>
+        <v>0</v>
       </c>
       <c r="P31">
         <v>0.7</v>
@@ -2864,7 +2594,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2896,8 +2626,8 @@
         <v>711</v>
       </c>
       <c r="K32" s="2">
-        <f t="shared" si="0"/>
-        <v>3120</v>
+        <f ca="1">IF(M32="Occupied",I32+J32,0)</f>
+        <v>0</v>
       </c>
       <c r="L32" s="2">
         <v>4818</v>
@@ -2906,12 +2636,12 @@
         <v>52</v>
       </c>
       <c r="N32" s="2">
-        <f t="shared" si="1"/>
-        <v>37440</v>
+        <f ca="1">K32*12</f>
+        <v>0</v>
       </c>
       <c r="O32">
-        <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F32,"M")</f>
+        <v>0</v>
       </c>
       <c r="P32">
         <v>0.8</v>
@@ -2920,7 +2650,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2931,7 +2661,7 @@
         <v>123</v>
       </c>
       <c r="D33" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E33" s="4">
         <v>45292</v>
@@ -2952,8 +2682,8 @@
         <v>226</v>
       </c>
       <c r="K33" s="2">
-        <f t="shared" si="0"/>
-        <v>4218</v>
+        <f ca="1">IF(M33="Occupied",I33+J33,0)</f>
+        <v>0</v>
       </c>
       <c r="L33" s="2">
         <v>7984</v>
@@ -2962,12 +2692,12 @@
         <v>52</v>
       </c>
       <c r="N33" s="2">
-        <f t="shared" si="1"/>
-        <v>50616</v>
+        <f ca="1">K33*12</f>
+        <v>0</v>
       </c>
       <c r="O33">
-        <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F33,"M")</f>
+        <v>0</v>
       </c>
       <c r="P33">
         <v>0.6</v>
@@ -2976,7 +2706,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3008,8 +2738,8 @@
         <v>579</v>
       </c>
       <c r="K34" s="2">
-        <f t="shared" ref="K34:K65" si="3">IF(M34="Occupied",I34+J34,0)</f>
-        <v>6210</v>
+        <f ca="1">IF(M34="Occupied",I34+J34,0)</f>
+        <v>0</v>
       </c>
       <c r="L34" s="2">
         <v>11262</v>
@@ -3018,12 +2748,12 @@
         <v>52</v>
       </c>
       <c r="N34" s="2">
-        <f t="shared" ref="N34:N51" si="4">K34*12</f>
-        <v>74520</v>
+        <f ca="1">K34*12</f>
+        <v>0</v>
       </c>
       <c r="O34">
-        <f t="shared" ref="O34:O51" ca="1" si="5">DATEDIF(TODAY(),F34,"M")</f>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F34,"M")</f>
+        <v>0</v>
       </c>
       <c r="P34">
         <v>0.8</v>
@@ -3032,7 +2762,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3043,7 +2773,7 @@
         <v>127</v>
       </c>
       <c r="D35" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E35" s="4">
         <v>45292</v>
@@ -3064,22 +2794,22 @@
         <v>299</v>
       </c>
       <c r="K35" s="2">
-        <f t="shared" si="3"/>
+        <f ca="1">IF(M35="Occupied",I35+J35,0)</f>
         <v>0</v>
       </c>
       <c r="L35" s="2">
         <v>7599</v>
       </c>
       <c r="M35" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="N35" s="2">
-        <f t="shared" si="4"/>
+        <f ca="1">K35*12</f>
         <v>0</v>
       </c>
       <c r="O35">
-        <f t="shared" ca="1" si="5"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F35,"M")</f>
+        <v>0</v>
       </c>
       <c r="P35">
         <v>0.7</v>
@@ -3088,7 +2818,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3120,8 +2850,8 @@
         <v>241</v>
       </c>
       <c r="K36" s="2">
-        <f t="shared" si="3"/>
-        <v>3477</v>
+        <f ca="1">IF(M36="Occupied",I36+J36,0)</f>
+        <v>0</v>
       </c>
       <c r="L36" s="2">
         <v>6472</v>
@@ -3130,12 +2860,12 @@
         <v>52</v>
       </c>
       <c r="N36" s="2">
-        <f t="shared" si="4"/>
-        <v>41724</v>
+        <f ca="1">K36*12</f>
+        <v>0</v>
       </c>
       <c r="O36">
-        <f t="shared" ca="1" si="5"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F36,"M")</f>
+        <v>0</v>
       </c>
       <c r="P36">
         <v>0.6</v>
@@ -3144,7 +2874,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3155,7 +2885,7 @@
         <v>131</v>
       </c>
       <c r="D37" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E37" s="4">
         <v>45292</v>
@@ -3176,8 +2906,8 @@
         <v>784</v>
       </c>
       <c r="K37" s="2">
-        <f t="shared" si="3"/>
-        <v>4565</v>
+        <f ca="1">IF(M37="Occupied",I37+J37,0)</f>
+        <v>0</v>
       </c>
       <c r="L37" s="2">
         <v>7562</v>
@@ -3186,12 +2916,12 @@
         <v>52</v>
       </c>
       <c r="N37" s="2">
-        <f t="shared" si="4"/>
-        <v>54780</v>
+        <f ca="1">K37*12</f>
+        <v>0</v>
       </c>
       <c r="O37">
-        <f t="shared" ca="1" si="5"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F37,"M")</f>
+        <v>0</v>
       </c>
       <c r="P37">
         <v>0.7</v>
@@ -3200,7 +2930,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3211,7 +2941,7 @@
         <v>133</v>
       </c>
       <c r="D38" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E38" s="4">
         <v>45292</v>
@@ -3232,8 +2962,8 @@
         <v>554</v>
       </c>
       <c r="K38" s="2">
-        <f t="shared" si="3"/>
-        <v>3803</v>
+        <f ca="1">IF(M38="Occupied",I38+J38,0)</f>
+        <v>0</v>
       </c>
       <c r="L38" s="2">
         <v>6498</v>
@@ -3242,12 +2972,12 @@
         <v>52</v>
       </c>
       <c r="N38" s="2">
-        <f t="shared" si="4"/>
-        <v>45636</v>
+        <f ca="1">K38*12</f>
+        <v>0</v>
       </c>
       <c r="O38">
-        <f t="shared" ca="1" si="5"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F38,"M")</f>
+        <v>0</v>
       </c>
       <c r="P38">
         <v>0.6</v>
@@ -3256,7 +2986,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3288,8 +3018,8 @@
         <v>104</v>
       </c>
       <c r="K39" s="2">
-        <f t="shared" si="3"/>
-        <v>4459</v>
+        <f ca="1">IF(M39="Occupied",I39+J39,0)</f>
+        <v>0</v>
       </c>
       <c r="L39" s="2">
         <v>8710</v>
@@ -3298,12 +3028,12 @@
         <v>52</v>
       </c>
       <c r="N39" s="2">
-        <f t="shared" si="4"/>
-        <v>53508</v>
+        <f ca="1">K39*12</f>
+        <v>0</v>
       </c>
       <c r="O39">
-        <f t="shared" ca="1" si="5"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F39,"M")</f>
+        <v>0</v>
       </c>
       <c r="P39">
         <v>0.7</v>
@@ -3312,7 +3042,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3323,7 +3053,7 @@
         <v>137</v>
       </c>
       <c r="D40" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E40" s="4">
         <v>45292</v>
@@ -3344,8 +3074,8 @@
         <v>368</v>
       </c>
       <c r="K40" s="2">
-        <f t="shared" si="3"/>
-        <v>4113</v>
+        <f ca="1">IF(M40="Occupied",I40+J40,0)</f>
+        <v>0</v>
       </c>
       <c r="L40" s="2">
         <v>7490</v>
@@ -3354,12 +3084,12 @@
         <v>52</v>
       </c>
       <c r="N40" s="2">
-        <f t="shared" si="4"/>
-        <v>49356</v>
+        <f ca="1">K40*12</f>
+        <v>0</v>
       </c>
       <c r="O40">
-        <f t="shared" ca="1" si="5"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F40,"M")</f>
+        <v>0</v>
       </c>
       <c r="P40">
         <v>0.6</v>
@@ -3368,7 +3098,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3400,8 +3130,8 @@
         <v>756</v>
       </c>
       <c r="K41" s="2">
-        <f t="shared" si="3"/>
-        <v>3684</v>
+        <f ca="1">IF(M41="Occupied",I41+J41,0)</f>
+        <v>0</v>
       </c>
       <c r="L41" s="2">
         <v>5856</v>
@@ -3410,12 +3140,12 @@
         <v>52</v>
       </c>
       <c r="N41" s="2">
-        <f t="shared" si="4"/>
-        <v>44208</v>
+        <f ca="1">K41*12</f>
+        <v>0</v>
       </c>
       <c r="O41">
-        <f t="shared" ca="1" si="5"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F41,"M")</f>
+        <v>0</v>
       </c>
       <c r="P41">
         <v>0.6</v>
@@ -3424,7 +3154,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3435,7 +3165,7 @@
         <v>141</v>
       </c>
       <c r="D42" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E42" s="4">
         <v>45292</v>
@@ -3456,22 +3186,22 @@
         <v>266</v>
       </c>
       <c r="K42" s="2">
-        <f t="shared" si="3"/>
+        <f ca="1">IF(M42="Occupied",I42+J42,0)</f>
         <v>0</v>
       </c>
       <c r="L42" s="2">
         <v>8122</v>
       </c>
       <c r="M42" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="N42" s="2">
-        <f t="shared" si="4"/>
+        <f ca="1">K42*12</f>
         <v>0</v>
       </c>
       <c r="O42">
-        <f t="shared" ca="1" si="5"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F42,"M")</f>
+        <v>0</v>
       </c>
       <c r="P42">
         <v>0.6</v>
@@ -3480,7 +3210,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17">
       <c r="A43">
         <v>42</v>
       </c>
@@ -3491,7 +3221,7 @@
         <v>143</v>
       </c>
       <c r="D43" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E43" s="4">
         <v>45292</v>
@@ -3512,8 +3242,8 @@
         <v>654</v>
       </c>
       <c r="K43" s="2">
-        <f t="shared" si="3"/>
-        <v>3001</v>
+        <f ca="1">IF(M43="Occupied",I43+J43,0)</f>
+        <v>0</v>
       </c>
       <c r="L43" s="2">
         <v>4694</v>
@@ -3522,12 +3252,12 @@
         <v>52</v>
       </c>
       <c r="N43" s="2">
-        <f t="shared" si="4"/>
-        <v>36012</v>
+        <f ca="1">K43*12</f>
+        <v>0</v>
       </c>
       <c r="O43">
-        <f t="shared" ca="1" si="5"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F43,"M")</f>
+        <v>0</v>
       </c>
       <c r="P43">
         <v>0.7</v>
@@ -3536,7 +3266,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17">
       <c r="A44">
         <v>43</v>
       </c>
@@ -3568,8 +3298,8 @@
         <v>720</v>
       </c>
       <c r="K44" s="2">
-        <f t="shared" si="3"/>
-        <v>6124</v>
+        <f ca="1">IF(M44="Occupied",I44+J44,0)</f>
+        <v>0</v>
       </c>
       <c r="L44" s="2">
         <v>10808</v>
@@ -3578,12 +3308,12 @@
         <v>52</v>
       </c>
       <c r="N44" s="2">
-        <f t="shared" si="4"/>
-        <v>73488</v>
+        <f ca="1">K44*12</f>
+        <v>0</v>
       </c>
       <c r="O44">
-        <f t="shared" ca="1" si="5"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F44,"M")</f>
+        <v>0</v>
       </c>
       <c r="P44">
         <v>0.9</v>
@@ -3592,7 +3322,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17">
       <c r="A45">
         <v>44</v>
       </c>
@@ -3624,8 +3354,8 @@
         <v>252</v>
       </c>
       <c r="K45" s="2">
-        <f t="shared" si="3"/>
-        <v>2496</v>
+        <f ca="1">IF(M45="Occupied",I45+J45,0)</f>
+        <v>0</v>
       </c>
       <c r="L45" s="2">
         <v>4488</v>
@@ -3634,12 +3364,12 @@
         <v>52</v>
       </c>
       <c r="N45" s="2">
-        <f t="shared" si="4"/>
-        <v>29952</v>
+        <f ca="1">K45*12</f>
+        <v>0</v>
       </c>
       <c r="O45">
-        <f t="shared" ca="1" si="5"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F45,"M")</f>
+        <v>0</v>
       </c>
       <c r="P45">
         <v>0.6</v>
@@ -3648,7 +3378,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17">
       <c r="A46">
         <v>45</v>
       </c>
@@ -3659,7 +3389,7 @@
         <v>149</v>
       </c>
       <c r="D46" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E46" s="4">
         <v>45292</v>
@@ -3680,8 +3410,8 @@
         <v>546</v>
       </c>
       <c r="K46" s="2">
-        <f t="shared" si="3"/>
-        <v>6153</v>
+        <f ca="1">IF(M46="Occupied",I46+J46,0)</f>
+        <v>0</v>
       </c>
       <c r="L46" s="2">
         <v>11214</v>
@@ -3690,12 +3420,12 @@
         <v>52</v>
       </c>
       <c r="N46" s="2">
-        <f t="shared" si="4"/>
-        <v>73836</v>
+        <f ca="1">K46*12</f>
+        <v>0</v>
       </c>
       <c r="O46">
-        <f t="shared" ca="1" si="5"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F46,"M")</f>
+        <v>0</v>
       </c>
       <c r="P46">
         <v>0.6</v>
@@ -3704,7 +3434,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17">
       <c r="A47">
         <v>46</v>
       </c>
@@ -3736,8 +3466,8 @@
         <v>437</v>
       </c>
       <c r="K47" s="2">
-        <f t="shared" si="3"/>
-        <v>5777</v>
+        <f ca="1">IF(M47="Occupied",I47+J47,0)</f>
+        <v>0</v>
       </c>
       <c r="L47" s="2">
         <v>10680</v>
@@ -3746,12 +3476,12 @@
         <v>52</v>
       </c>
       <c r="N47" s="2">
-        <f t="shared" si="4"/>
-        <v>69324</v>
+        <f ca="1">K47*12</f>
+        <v>0</v>
       </c>
       <c r="O47">
-        <f t="shared" ca="1" si="5"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F47,"M")</f>
+        <v>0</v>
       </c>
       <c r="P47">
         <v>0.6</v>
@@ -3760,7 +3490,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17">
       <c r="A48">
         <v>47</v>
       </c>
@@ -3771,7 +3501,7 @@
         <v>153</v>
       </c>
       <c r="D48" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E48" s="4">
         <v>45292</v>
@@ -3792,8 +3522,8 @@
         <v>437</v>
       </c>
       <c r="K48" s="2">
-        <f t="shared" si="3"/>
-        <v>5307</v>
+        <f ca="1">IF(M48="Occupied",I48+J48,0)</f>
+        <v>0</v>
       </c>
       <c r="L48" s="2">
         <v>9740</v>
@@ -3802,12 +3532,12 @@
         <v>52</v>
       </c>
       <c r="N48" s="2">
-        <f t="shared" si="4"/>
-        <v>63684</v>
+        <f ca="1">K48*12</f>
+        <v>0</v>
       </c>
       <c r="O48">
-        <f t="shared" ca="1" si="5"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F48,"M")</f>
+        <v>0</v>
       </c>
       <c r="P48">
         <v>0.7</v>
@@ -3816,7 +3546,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17">
       <c r="A49">
         <v>48</v>
       </c>
@@ -3827,7 +3557,7 @@
         <v>155</v>
       </c>
       <c r="D49" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E49" s="4">
         <v>45292</v>
@@ -3848,22 +3578,22 @@
         <v>275</v>
       </c>
       <c r="K49" s="2">
-        <f t="shared" si="3"/>
+        <f ca="1">IF(M49="Occupied",I49+J49,0)</f>
         <v>0</v>
       </c>
       <c r="L49" s="2">
         <v>7899</v>
       </c>
       <c r="M49" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="N49" s="2">
-        <f t="shared" si="4"/>
+        <f ca="1">K49*12</f>
         <v>0</v>
       </c>
       <c r="O49">
-        <f t="shared" ca="1" si="5"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F49,"M")</f>
+        <v>0</v>
       </c>
       <c r="P49">
         <v>0.8</v>
@@ -3872,7 +3602,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17">
       <c r="A50">
         <v>49</v>
       </c>
@@ -3883,7 +3613,7 @@
         <v>157</v>
       </c>
       <c r="D50" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E50" s="4">
         <v>45292</v>
@@ -3904,8 +3634,8 @@
         <v>514</v>
       </c>
       <c r="K50" s="2">
-        <f t="shared" si="3"/>
-        <v>2573</v>
+        <f ca="1">IF(M50="Occupied",I50+J50,0)</f>
+        <v>0</v>
       </c>
       <c r="L50" s="2">
         <v>4118</v>
@@ -3914,12 +3644,12 @@
         <v>52</v>
       </c>
       <c r="N50" s="2">
-        <f t="shared" si="4"/>
-        <v>30876</v>
+        <f ca="1">K50*12</f>
+        <v>0</v>
       </c>
       <c r="O50">
-        <f t="shared" ca="1" si="5"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F50,"M")</f>
+        <v>0</v>
       </c>
       <c r="P50">
         <v>0.6</v>
@@ -3928,7 +3658,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17">
       <c r="A51">
         <v>50</v>
       </c>
@@ -3960,8 +3690,8 @@
         <v>308</v>
       </c>
       <c r="K51" s="2">
-        <f t="shared" si="3"/>
-        <v>5198</v>
+        <f ca="1">IF(M51="Occupied",I51+J51,0)</f>
+        <v>0</v>
       </c>
       <c r="L51" s="2">
         <v>9780</v>
@@ -3970,12 +3700,12 @@
         <v>52</v>
       </c>
       <c r="N51" s="2">
-        <f t="shared" si="4"/>
-        <v>62376</v>
+        <f ca="1">K51*12</f>
+        <v>0</v>
       </c>
       <c r="O51">
-        <f t="shared" ca="1" si="5"/>
-        <v>26</v>
+        <f ca="1">DATEDIF(TODAY(),F51,"M")</f>
+        <v>0</v>
       </c>
       <c r="P51">
         <v>0.7</v>
@@ -3986,36 +3716,38 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="M1:M1048576">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Vacant">
+    <cfRule type="containsText" dxfId="0" operator="containsText" text="Vacant" priority="1">
       <formula>NOT(ISERROR(SEARCH("Vacant",M1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter alignWithMargins="0"/>
+  <headerFooter scaleWithDoc="1" alignWithMargins="0" differentFirst="0" differentOddEven="0"/>
+  <extLst/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr/>
   <dimension ref="A1:M2"/>
-  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr customHeight="true" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" customWidth="1"/>
-    <col min="2" max="2" width="13.21875" customWidth="1"/>
-    <col min="3" max="3" width="11.21875" customWidth="1"/>
-    <col min="4" max="4" width="19.6640625" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" customWidth="1"/>
-    <col min="6" max="6" width="15.5546875" customWidth="1"/>
-    <col min="7" max="7" width="19.21875" customWidth="1"/>
-    <col min="8" max="8" width="14.44140625" customWidth="1"/>
-    <col min="9" max="9" width="17.44140625" customWidth="1"/>
+    <col min="1" max="1" width="9.84765625" customWidth="1"/>
+    <col min="2" max="2" width="13.27734375" customWidth="1"/>
+    <col min="3" max="3" width="11.27734375" customWidth="1"/>
+    <col min="4" max="4" width="19.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" customWidth="1"/>
+    <col min="7" max="7" width="19.27734375" customWidth="1"/>
+    <col min="8" max="8" width="14.41796875" customWidth="1"/>
+    <col min="9" max="9" width="17.41796875" customWidth="1"/>
     <col min="10" max="10" width="17" customWidth="1"/>
-    <col min="11" max="11" width="19.6640625" customWidth="1"/>
-    <col min="12" max="12" width="12.44140625" customWidth="1"/>
-    <col min="13" max="13" width="13.6640625" customWidth="1"/>
+    <col min="11" max="11" width="19.7109375" customWidth="1"/>
+    <col min="12" max="12" width="12.41796875" customWidth="1"/>
+    <col min="13" max="13" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>160</v>
       </c>
@@ -4056,62 +3788,63 @@
         <v>172</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13">
       <c r="A2">
-        <f>COUNTA('Rent Roll Data'!A2:A51)</f>
-        <v>50</v>
+        <f ca="1">COUNTA('Rent Roll Data'!A2:A51)</f>
+        <v>0</v>
       </c>
       <c r="B2">
-        <f>COUNTIF('Rent Roll Data'!M2:M51,"Occupied")</f>
-        <v>43</v>
+        <f ca="1">COUNTIF('Rent Roll Data'!M2:M51,"Occupied")</f>
+        <v>0</v>
       </c>
       <c r="C2">
-        <f>COUNTIF('Rent Roll Data'!M2:M51,"Vacant")</f>
-        <v>7</v>
+        <f ca="1">COUNTIF('Rent Roll Data'!M2:M51,"Vacant")</f>
+        <v>0</v>
       </c>
       <c r="D2" s="5">
-        <f>B2/A2</f>
-        <v>0.86</v>
+        <f ca="1">B2/A2</f>
+        <v>0</v>
       </c>
       <c r="E2" s="2">
-        <f>SUM('Rent Roll Data'!K2:K51)</f>
-        <v>195139</v>
+        <f ca="1">SUM('Rent Roll Data'!K2:K51)</f>
+        <v>0</v>
       </c>
       <c r="F2" s="2">
-        <f>SUM('Rent Roll Data'!N2:N51)</f>
-        <v>2341668</v>
+        <f ca="1">SUM('Rent Roll Data'!N2:N51)</f>
+        <v>0</v>
       </c>
       <c r="G2" s="2">
         <f ca="1">AVERAGE('Rent Roll Data'!A11:AX11)</f>
-        <v>14934.408333333333</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <f>MAX('Rent Roll Data'!H2:H51)</f>
-        <v>3351</v>
+        <f ca="1">MAX('Rent Roll Data'!H2:H51)</f>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <f>MAX('Rent Roll Data'!N2:N51)</f>
-        <v>77088</v>
+        <f ca="1">MAX('Rent Roll Data'!N2:N51)</f>
+        <v>0</v>
       </c>
       <c r="J2" s="2">
-        <f>'Property Information'!S2</f>
-        <v>450000</v>
+        <f ca="1">'Property Information'!S2</f>
+        <v>0</v>
       </c>
       <c r="K2" s="2">
-        <f>'Property Information'!T2</f>
-        <v>120000</v>
+        <f ca="1">'Property Information'!T2</f>
+        <v>0</v>
       </c>
       <c r="L2" s="2">
-        <f>F2-(J2+K2)</f>
-        <v>1771668</v>
+        <f ca="1">F2-(J2+K2)</f>
+        <v>0</v>
       </c>
       <c r="M2" s="2">
-        <f>L2/'Property Information'!R2</f>
-        <v>27256430.769230768</v>
+        <f ca="1">L2/'Property Information'!R2</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter alignWithMargins="0"/>
+  <headerFooter scaleWithDoc="1" alignWithMargins="0" differentFirst="0" differentOddEven="0"/>
+  <extLst/>
 </worksheet>
 </file>